--- a/param_extraction/data/params_for_review.xlsx
+++ b/param_extraction/data/params_for_review.xlsx
@@ -55,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,17 +63,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,7 +464,7 @@
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
@@ -1127,22 +1143,20 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>may cause an illegal-instruction exception or may return a constant value</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>counters.adoc</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>may cause an illegal-instruction exception or may return a constant value</t>
-        </is>
+      <c r="G16" s="3" t="n">
+        <v>191</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>Accessing an unimplemented counter may cause an illegal-instruction exception or may return a constant value.</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1174,22 +1188,20 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>the counter may return a constant value</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>counters.adoc</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>the counter may return a constant value</t>
-        </is>
+      <c r="G17" s="3" t="n">
+        <v>192</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>If the configuration used to select the events counted by a counter is misconfigured, the counter may return a constant value.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1221,22 +1233,20 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>an implementation may make VSXL be a read-only field</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>an implementation may make VSXL be a read-only field</t>
-        </is>
+      <c r="G18" s="3" t="n">
+        <v>244</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>In particular, an implementation may make VSXL be a read-only field whose value always ensures that VSXLEN=HSXLEN.</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1268,22 +1278,20 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
+          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
-        </is>
+      <c r="G19" s="3" t="n">
+        <v>260</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1315,22 +1323,20 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>An implementation may make field UBE be a read-only copy</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>An implementation may make field UBE be a read-only copy</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>1226</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>An implementation may make field UBE be a read-only copy of `hstatus`.VSBE.</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1362,22 +1368,20 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
+          <t>An implementation can choose to subset the delegatable traps</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>An implementation can choose to subset the delegatable traps</t>
-        </is>
+      <c r="G21" s="3" t="n">
+        <v>1310</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>An implementation can choose to subset the delegatable traps, with the supported delegatable bits found by writing one to every bit location, then reading back the value in `medeleg` or `mideleg` to see which bit positions hold a one.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1409,22 +1413,20 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>may be writable or may be read-only</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>may be writable or may be read-only</t>
-        </is>
+      <c r="G22" s="3" t="n">
+        <v>1395</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>Each individual bit in register `mip` may be writable or may be read-only.</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1456,22 +1458,20 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
+          <t>Not all physical address bits may be implemented</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Not all physical address bits may be implemented</t>
-        </is>
+      <c r="G23" s="3" t="n">
+        <v>3395</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>Not all physical address bits may be implemented, and so the `pmpaddr` registers are WARL.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1503,22 +1503,20 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t>implementations may convert an invalid address</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
           <t>rnmi.adoc</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>implementations may convert an invalid address</t>
-        </is>
+      <c r="G24" s="3" t="n">
+        <v>62</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>Prior to writing `mnepc`, implementations may convert an invalid address into some other invalid address that `mnepc` is capable of holding.</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1550,22 +1548,20 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t>may implement `mseccfg` such that `[s,u]seed` is a read-only constant value</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t>scalar-crypto.adoc</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>may implement `mseccfg` such that `[s,u]seed` is a read-only constant value</t>
-        </is>
+      <c r="G25" s="3" t="n">
+        <v>3750</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1597,22 +1593,20 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
+          <t>implementation-specific which DEPTH value(s) are supported</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>implementation-specific which DEPTH value(s) are supported</t>
-        </is>
+      <c r="G26" s="3" t="n">
+        <v>189</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>It is implementation-specific which DEPTH value(s) are supported.</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1644,22 +1638,20 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
+          <t>The optional MISP bit</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>The optional MISP bit</t>
-        </is>
+      <c r="G27" s="3" t="n">
+        <v>295</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -1691,22 +1683,20 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
+          <t>may optionally include a count of CPU cycles</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>may optionally include a count of CPU cycles</t>
-        </is>
+      <c r="G28" s="3" t="n">
+        <v>612</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1738,22 +1728,20 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
+          <t>may implement 0..4 exponent bits in CCE</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>may implement 0..4 exponent bits in CCE</t>
-        </is>
+      <c r="G29" s="3" t="n">
+        <v>638</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE.</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -1785,22 +1773,20 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
+          <t>When the optional `__x__ctrctl`.RASEMU bit is implemented</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>When the optional `__x__ctrctl`.RASEMU bit is implemented</t>
-        </is>
+      <c r="G30" s="3" t="n">
+        <v>669</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -1832,22 +1818,20 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
+          <t>may or may not raise an illegal-instruction or virtual-instruction exception</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
           <t>smstateen.adoc</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>may or may not raise an illegal-instruction or virtual-instruction exception</t>
-        </is>
+      <c r="G31" s="3" t="n">
+        <v>103</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>When a `stateen` CSR prevents access to state for a privilege mode, attempting to execute in that privilege mode an instruction that _implicitly_ updates the state without reading it may or may not raise an illegal-instruction or virtual-instruction exception.</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -1879,22 +1863,20 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
+          <t>an implementation may make UXL be a read-only field</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>an implementation may make UXL be a read-only field</t>
-        </is>
+      <c r="G32" s="3" t="n">
+        <v>134</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>When SXLEN=64, it is a *WARL* field that encodes the current value of UXLEN. In particular, an implementation may make UXL be a read-only field whose value always ensures that UXLEN=SXLEN.</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -1926,22 +1908,20 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten</t>
-        </is>
+      <c r="G33" s="3" t="n">
+        <v>149</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -1973,22 +1953,20 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
+          <t>An implementation may make UBE be a read-only field</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>An implementation may make UBE be a read-only field</t>
-        </is>
+      <c r="G34" s="3" t="n">
+        <v>221</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>An implementation may make UBE be a read-only field that always specifies the same endianness as for S-mode.</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2020,22 +1998,20 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
+          <t>may be writable or may be read-only</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>may be writable or may be read-only</t>
-        </is>
+      <c r="G35" s="3" t="n">
+        <v>434</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>Each individual bit in register `sip` may be writable or may be read-only.</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2067,22 +2043,20 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
+          <t>may not be implemented</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>may not be implemented</t>
-        </is>
+      <c r="G36" s="3" t="n">
+        <v>520</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>Each standard interrupt type (SEI, STI, SSI, or LCOFI) may not be implemented, in which case the corresponding interrupt-pending and interrupt-enable bits are read-only zeros.</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2114,22 +2088,20 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
+          <t>the implementation may make FIOM read-only zero</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>the implementation may make FIOM read-only zero</t>
-        </is>
+      <c r="G37" s="3" t="n">
+        <v>1001</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2161,22 +2133,20 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
+          <t>optionally relaxes this alignment requirement</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
           <t>zalasr.adoc</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>optionally relaxes this alignment requirement</t>
-        </is>
+      <c r="G38" s="3" t="n">
+        <v>23</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>The misaligned atomicity granule PMA, defined in Volume II of this manual, optionally relaxes this alignment requirement.</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -2208,22 +2178,20 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
+          <t>may define that accesses to certain CSRs are strongly ordered</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
           <t>zicsr.adoc</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>may define that accesses to certain CSRs are strongly ordered</t>
-        </is>
+      <c r="G39" s="3" t="n">
+        <v>244</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>The hardware platform may define that accesses to certain CSRs are strongly ordered, as defined by the Memory-Ordering PMAs section in Volume II of this manual.</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">

--- a/param_extraction/data/params_for_review.xlsx
+++ b/param_extraction/data/params_for_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="params_for_review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'params_for_review'!$A$1:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'params_for_review'!$A$1:$N$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,7 +84,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -457,18 +457,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,10 +514,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>norm_tag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tagged</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>refers_to_csr_field_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>refers_to_warl</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cross_chapter_dup</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>excerpt</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mentor_comment</t>
         </is>
@@ -554,12 +584,29 @@
           <t>416</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>When such a HINT is executed with XLEN &lt; MXLEN and bits MXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits MXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -597,12 +644,29 @@
           <t>141</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -642,10 +706,31 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>norm:xret_clr_lr_resv</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>If the A extension is supported, the __x__RET instruction is allowed to clear any outstanding LR address reservation but is not required to.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -683,12 +768,29 @@
           <t>1543</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>WFI is available in all privileged modes, and optionally available to U-mode.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -728,10 +830,31 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>norm:vtw_virtinstr_param</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -771,10 +894,31 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>norm:mstatus_tw_always_illegal</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>An implementation may have WFI always raise an illegal-instruction exception in modes less privileged than M when TW=1, even if there are pending globally-disabled interrupts when the instruction is executed.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -812,12 +956,29 @@
           <t>3697</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -857,10 +1018,31 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>norm:ctrtarget_misp</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -900,10 +1082,31 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>norm:ctrdata_cc_supported_param</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.  The elapsed cycle count value is represented by the CC field, which has a 12-bit mantissa component (Cycle Count Mantissa, or CCM) and a 4-bit exponent component (Cycle Count Exponent, or CCE).</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -943,10 +1146,31 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>norm:ccounter_impl</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE. Unimplemented CCE bits are read-only 0.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -986,10 +1210,31 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>norm:ctrctl_rasemu_op</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1029,10 +1274,31 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>norm:sctrdepth-depth_param</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>It is implementation-specific which DEPTH value(s) are supported.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1072,10 +1338,31 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>norm:menvcfg_fiom_rdonly0_ok</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>If S-mode is not supported, or if `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1113,12 +1400,33 @@
           <t>706</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>YES: machine.adoc, supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1151,15 +1459,38 @@
           <t>counters.adoc</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>191</v>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>norm:hpm_unimplemented_counter_access</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
           <t>Accessing an unimplemented counter may cause an illegal-instruction exception or may return a constant value.</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>WARL parameter:  returning a constant value implies implemented, so which counters are implemented is the parameter, If unimplmented, requires illegal inst trap (NOT unspecified)</t>
         </is>
@@ -1196,15 +1527,38 @@
           <t>counters.adoc</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>192</v>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>norm:hpm_misconfigured_event_behavior</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
           <t>If the configuration used to select the events counted by a counter is misconfigured, the counter may return a constant value.</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (only tested if Ssstrict is implemented, else is unspeciifed</t>
         </is>
@@ -1241,15 +1595,38 @@
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>244</v>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
+          <t>norm:vsxl_ro_param</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
           <t>In particular, an implementation may make VSXL be a read-only field whose value always ensures that VSXLEN=HSXLEN.</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value is the the value of some other state bit</t>
         </is>
@@ -1286,15 +1663,38 @@
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>260</v>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
+          <t>norm:vtw_virtinstr_param</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
           <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>parameter: raise virt inst, or just wait?</t>
         </is>
@@ -1331,15 +1731,34 @@
           <t>hypervisor.adoc</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>1226</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>1226</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>An implementation may make field UBE be a read-only copy of `hstatus`.VSBE.</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>parameter: new WARL  behavior! (ReadOnly, but value is the the value of some other state bit)</t>
         </is>
@@ -1376,15 +1795,38 @@
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>1310</v>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>1310</t>
+        </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
+          <t>norm:medeleg_mideleg_warl</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
           <t>An implementation can choose to subset the delegatable traps, with the supported delegatable bits found by writing one to every bit location, then reading back the value in `medeleg` or `mideleg` to see which bit positions hold a one.</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
         </is>
@@ -1421,15 +1863,38 @@
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>1395</v>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>norm:mip_bits_wr_or_rdonly</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t>Each individual bit in register `mip` may be writable or may be read-only.</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
         </is>
@@ -1466,15 +1931,38 @@
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>3395</v>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
+          <t>norm:pmp_addr_warl</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
           <t>Not all physical address bits may be implemented, and so the `pmpaddr` registers are WARL.</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL  (number of implemented address bits; conditional on or priv mode and xSATP.mode (VA vs. PA)</t>
         </is>
@@ -1511,15 +1999,38 @@
           <t>rnmi.adoc</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>62</v>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
+          <t>norm:mnepc_invalid_convert</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
           <t>Prior to writing `mnepc`, implementations may convert an invalid address into some other invalid address that `mnepc` is capable of holding.</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="N24" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior ( but depends on definition of "invalid". Implies implemented&lt;full width.)</t>
         </is>
@@ -1556,15 +2067,34 @@
           <t>scalar-crypto.adoc</t>
         </is>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>3750</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
         </is>
@@ -1601,15 +2131,38 @@
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>189</v>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
+          <t>norm:sctrdepth-depth_param</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t>It is implementation-specific which DEPTH value(s) are supported.</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (range value, or set)</t>
         </is>
@@ -1646,15 +2199,38 @@
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>295</v>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
+          <t>norm:ctrtarget_misp</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value is either fixed 0 or the the value of some *internal* status  bit)</t>
         </is>
@@ -1691,15 +2267,38 @@
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>612</v>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
+          <t>norm:ctrdata_cc_supported_param</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr"/>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
           <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="N28" s="3" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
@@ -1736,15 +2335,38 @@
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>638</v>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
+          <t>norm:ccounter_impl</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE.</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
         <is>
           <t>parameter (also in top-14 above)</t>
         </is>
@@ -1781,15 +2403,38 @@
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>669</v>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
+          <t>norm:ctrctl_rasemu_op</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
           <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="N30" s="3" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
@@ -1826,15 +2471,34 @@
           <t>smstateen.adoc</t>
         </is>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>When a `stateen` CSR prevents access to state for a privilege mode, attempting to execute in that privilege mode an instruction that _implicitly_ updates the state without reading it may or may not raise an illegal-instruction or virtual-instruction exception.</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
         <is>
           <t>parameter (trap or not; which kind of trap is defined elsewhere)</t>
         </is>
@@ -1871,15 +2535,34 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>When SXLEN=64, it is a *WARL* field that encodes the current value of UXLEN. In particular, an implementation may make UXL be a read-only field whose value always ensures that UXLEN=SXLEN.</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value includes the value of sother state bit)</t>
         </is>
@@ -1916,15 +2599,34 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
@@ -1961,15 +2663,34 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t>An implementation may make UBE be a read-only field that always specifies the same endianness as for S-mode.</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="N34" s="3" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value includes the value of some state  bit)</t>
         </is>
@@ -2006,15 +2727,38 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>434</v>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
+          <t>norm:sip_acc</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
           <t>Each individual bit in register `sip` may be writable or may be read-only.</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
         <is>
           <t>WARL parameter (RW, RdOnly0/1)</t>
         </is>
@@ -2051,15 +2795,34 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>520</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>Each standard interrupt type (SEI, STI, SSI, or LCOFI) may not be implemented, in which case the corresponding interrupt-pending and interrupt-enable bits are read-only zeros.</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
         <is>
           <t>WARL parameter (RW, RdOnly0)</t>
         </is>
@@ -2096,15 +2859,38 @@
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>YES: machine.adoc, supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
         <is>
           <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
         <is>
           <t>WARL parameter: conditional on mode  (also in top-14 above)</t>
         </is>
@@ -2141,15 +2927,42 @@
           <t>zalasr.adoc</t>
         </is>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>23</v>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
+          <t>norm:zalasr_misaligned_pma_relax</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>YES: a-st-ext.adoc, zalasr.adoc</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
           <t>The misaligned atomicity granule PMA, defined in Volume II of this manual, optionally relaxes this alignment requirement.</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>parameter: (existence &amp; value of atomicity granule)</t>
         </is>
@@ -2186,22 +2999,45 @@
           <t>zicsr.adoc</t>
         </is>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>244</v>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
+          <t>norm:csr_strongly_ordered</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
           <t>The hardware platform may define that accesses to certain CSRs are strongly ordered, as defined by the Memory-Ordering PMAs section in Volume II of this manual.</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
         <is>
           <t>parameter: memory ordering PMA value(s)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I39"/>
+  <autoFilter ref="A1:N39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/param_extraction/data/params_for_review.xlsx
+++ b/param_extraction/data/params_for_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="params_for_review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'params_for_review'!$A$1:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'params_for_review'!$A$1:$O$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +95,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,23 +465,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,14 +523,14 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>tagged</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>norm_tag</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tagged</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>refers_to_csr_field_value</t>
@@ -534,15 +543,20 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>in_intro_section</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>cross_chapter_dup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>excerpt</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>mentor_comment</t>
         </is>
@@ -551,17 +565,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HINT_XLEN_REDUCTION_BEHAVIOR</t>
+          <t>CTR_CTRDATA_TYPE_IMPLEMENTED</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -571,117 +585,131 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>it is implementation-defined whether bits MXLEN..XLEN of the destination register are unchanged or are overwritten</t>
+          <t>all fields within it are optional</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>smctr.adoc</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>norm:ctrdata_sz_acc</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>When such a HINT is executed with XLEN &lt; MXLEN and bits MXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits MXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>The `ctrdata` register contains metadata for the recorded transfer. This register must be implemented, though all fields within it are optional. Unimplemented fields are read-only 0.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HINT_SXLEN_DEST_REG_BEHAVIOR</t>
+          <t>HIP_BIT_WRITABLE</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>bitmask</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten</t>
+          <t>may be writable or may be read-only</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>supervisor.adoc</t>
+          <t>hypervisor.adoc</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>If bit _i_ of `sie` is read-only zero, the same bit in register `hip` may be writable or may be read-only.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>XRET_CLEARS_LR_RESERVATION</t>
+          <t>LCOFI_MIDELEG_HIDELEG_WRITABLE</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -691,29 +719,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>is allowed to clear any outstanding LR address reservation but is not required to</t>
+          <t>It is optional whether the LCOFI bit (bit 13) in each of mideleg and hideleg ... is implemented and writable</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>smcdeleg.adoc</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>norm:xret_clr_lr_resv</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>no</t>
@@ -724,23 +748,28 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>If the A extension is supported, the __x__RET instruction is allowed to clear any outstanding LR address reservation but is not required to.</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>It is optional whether the LCOFI bit (bit 13) in each of mideleg and hideleg, which allows all LCOFIs to be delegated to S-mode and VS-mode, respectively, is implemented and writable.</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>WFI_U_MODE</t>
+          <t>PMA_IDEMPOTENT_IMPLICIT_READ_SIZE</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -750,12 +779,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>optionally available to U-mode</t>
+          <t>is implementation-defined</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -765,13 +794,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>norm:pma_idp_implicit_sz</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -784,28 +817,33 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>WFI is available in all privileged modes, and optionally available to U-mode.</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>The size of these naturally aligned power-of-2 regions is implementation-defined, but, for systems with page-based virtual memory, must not exceed the smallest supported page size.</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>VTW_WFI_ALWAYS_TRAP</t>
+          <t>SEPC_INVALID_ADDR_BEHAVIOR</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -815,91 +853,92 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
+          <t>implementations may convert an invalid address into some other invalid address that `sepc` is capable of holding</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>hypervisor.adoc</t>
+          <t>supervisor.adoc</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>norm:vtw_virtinstr_param</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>`sepc` is a *WARL* register that must be able to hold all valid virtual addresses. It need not be capable of holding all possible invalid addresses. Prior to writing `sepc`, implementations may convert an invalid address into some other invalid address that `sepc` is capable of holding.</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>WFI_TW_ALWAYS_ILLEGAL</t>
+          <t>SISELECT_WIDTH</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>An implementation may have WFI always raise an illegal-instruction exception</t>
+          <t>Only if such an extension is implemented will `siselect` be required to support larger values</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
+          <t>indirect-csr.adoc</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>138</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>norm:mstatus_tw_always_illegal</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:siselect_min_range</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -912,59 +951,68 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>An implementation may have WFI always raise an illegal-instruction exception in modes less privileged than M when TW=1, even if there are pending globally-disabled interrupts when the instruction is executed.</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>The `siselect` register will support the value range 0..0xFFF at a minimum. A future extension may define a value range outside of this minimum range. Only if such an extension is implemented will `siselect` be required to support larger values.</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SSEED_USEED_WRITABLE</t>
+          <t>VSISELECT_WIDTH</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`</t>
+          <t>Only if such an extension is implemented will `vsiselect` be required to support larger values</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>scalar-crypto.adoc</t>
+          <t>indirect-csr.adoc</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>norm:vsiselect_min_range</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -972,28 +1020,33 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>The `vsiselect` register will support the value range 0..0xFFF at a minimum. A future extension may define a value range outside of this minimum range. Only if such an extension is implemented will `vsiselect` be required to support larger values.</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CTR_MISP_IMPLEMENTED</t>
+          <t>WFI_NOP_BEHAVIOR</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1003,27 +1056,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>optional MISP bit</t>
+          <t>Implementations are permitted to resume execution for any reason</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>smctr.adoc</t>
+          <t>machine.adoc</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>norm:ctrtarget_misp</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:wfi_resume_reason</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1033,31 +1086,36 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Implementations are permitted to resume execution for any reason, even if an enabled interrupt has not become pending. Hence, a legal implementation is to simply implement the WFI instruction as a NOP.</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1. V4 — for review</t>
+          <t>0. NEW findings (for review)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CTR_CYCLE_COUNT_IMPLEMENTED</t>
+          <t>ZCMP_PUSH_BUS_FAULT_HANDLING</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_DIRECT</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1067,32 +1125,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>may optionally include a count of CPU cycles</t>
+          <t>platform defined whether the core implementation waits for the bus responses</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>smctr.adoc</t>
+          <t>zc.adoc</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>norm:ctrdata_cc_supported_param</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1100,343 +1154,371 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.  The elapsed cycle count value is represented by the CC field, which has a 12-bit mantissa component (Cycle Count Mantissa, or CCM) and a 4-bit exponent component (Cycle Count Exponent, or CCE).</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>It is platform defined whether the core implementation waits for the bus responses before continuing to the final stage of the sequence, or handles errors responses after completing the PUSH instruction.</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>1. V4 — for review</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CTR_CCE_WIDTH</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>NORM_CSR_RW</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>may implement 0..4 exponent bits in CCE</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>smctr.adoc</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>norm:ccounter_impl</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE. Unimplemented CCE bits are read-only 0.</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>HINT_XLEN_REDUCTION_BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>it is implementation-defined whether bits MXLEN..XLEN of the destination register are unchanged or are overwritten</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>416</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>When such a HINT is executed with XLEN &lt; MXLEN and bits MXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits MXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>parameter ! (but hints should not update state; so this implies hints don't apply to currently non-visible state!!!</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>1. V4 — for review</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CTR_RASEMU_IMPLEMENTED</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>NORM_CSR_RW</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>HINT_SXLEN_DEST_REG_BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>optional `__x__ctrctl`.RASEMU bit is implemented</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>smctr.adoc</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>norm:ctrctl_rasemu_op</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>parameter ! (but hints should not update state; so this implies hints don't apply to currently non-visible state!!!</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>1. V4 — for review</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CTR_SUPPORTED_DEPTHS</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>NORM_CSR_WARL</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>set</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>implementation-specific which DEPTH value(s) are supported</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>smctr.adoc</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>norm:sctrdepth-depth_param</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>It is implementation-specific which DEPTH value(s) are supported.</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>XRET_CLEARS_LR_RESERVATION</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>is allowed to clear any outstanding LR address reservation but is not required to</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>1535</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>norm:xret_clr_lr_resv</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>If the A extension is supported, the __x__RET instruction is allowed to clear any outstanding LR address reservation but is not required to.</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>parameter (though could be non-deterministic)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>1. V4 — for review</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>MENVCFG_FIOM_READONLY</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>NORM_CSR_RW</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>WFI_U_MODE</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>the implementation may make FIOM read-only zero</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>optionally available to U-mode</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1455</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>norm:menvcfg_fiom_rdonly0_ok</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>If S-mode is not supported, or if `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="G14" s="3" t="n">
+        <v>1543</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>WFI is available in all privileged modes, and optionally available to U-mode.</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>duplicate (see below, which give the exact conditions)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1. V4 — for review</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SENVCFG_FIOM_ACCESS</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>NORM_CSR_RW</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VTW_WFI_ALWAYS_TRAP</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>the implementation may make FIOM read-only zero</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>supervisor.adoc</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>YES: machine.adoc, supervisor.adoc</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>hypervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>norm:vtw_virtinstr_param</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>parameter: the choice here is illegal-inst vs. wakeup even if interrupt occurs withinthe time limit</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>HPM_UNIMPLEMENTED_ACCESS_BEHAVIOR</t>
+          <t>WFI_TW_ALWAYS_ILLEGAL</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1446,32 +1528,30 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>may cause an illegal-instruction exception or may return a constant value</t>
+          <t>An implementation may have WFI always raise an illegal-instruction exception</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>counters.adoc</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>617</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>norm:hpm_unimplemented_counter_access</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:mstatus_tw_always_illegal</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1484,32 +1564,37 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Accessing an unimplemented counter may cause an illegal-instruction exception or may return a constant value.</t>
-        </is>
-      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>WARL parameter:  returning a constant value implies implemented, so which counters are implemented is the parameter, If unimplmented, requires illegal inst trap (NOT unspecified)</t>
+          <t>An implementation may have WFI always raise an illegal-instruction exception in modes less privileged than M when TW=1, even if there are pending globally-disabled interrupts when the instruction is executed.</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>parameter: the choice here is illegal-inst vs. wakeup even if interrupt occurs withinthe time limit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>HPM_MISCONFIGURED_BEHAVIOR</t>
+          <t>SSEED_USEED_WRITABLE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1519,32 +1604,26 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>the counter may return a constant value</t>
+          <t>may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>counters.adoc</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+          <t>scalar-crypto.adoc</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>3697</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>norm:hpm_misconfigured_event_behavior</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1552,27 +1631,32 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>If the configuration used to select the events counted by a counter is misconfigured, the counter may return a constant value.</t>
-        </is>
-      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>parameter: WARL behavior (only tested if Ssstrict is implemented, else is unspeciifed</t>
+          <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>WARL parameter (RW, RdOnly0) even though not explicitly WARL)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>VSXL_RO_PARAM</t>
+          <t>CTR_MISP_IMPLEMENTED</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1587,27 +1671,25 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>an implementation may make VSXL be a read-only field</t>
+          <t>optional MISP bit</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>hypervisor.adoc</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
+          <t>smctr.adoc</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>330</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>norm:vsxl_ro_param</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:ctrtarget_misp</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1617,35 +1699,40 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>In particular, an implementation may make VSXL be a read-only field whose value always ensures that VSXLEN=HSXLEN.</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>new WARL parameter behavior! (ReadOnly, but value is the the value of some other state bit</t>
+          <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>arguably WARL behavior: either 0 or a copy of an internal mispredict state bit.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>VTW_VIRTINSTR_PARAM</t>
+          <t>CTR_CYCLE_COUNT_IMPLEMENTED</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>NORM_DIRECT</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1655,27 +1742,25 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
+          <t>may optionally include a count of CPU cycles</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>hypervisor.adoc</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+          <t>smctr.adoc</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>618</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>norm:vtw_virtinstr_param</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:ctrdata_cc_supported_param</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1688,27 +1773,32 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
-        </is>
-      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr"/>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>parameter: raise virt inst, or just wait?</t>
+          <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.  The elapsed cycle count value is represented by the CC field, which has a 12-bit mantissa component (Cycle Count Mantissa, or CCM) and a 4-bit exponent component (Cycle Count Exponent, or CCE).</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>possibly a parameter; depends on whether there is some other state bit that controls this</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>VSSTATUS_UBE_PARAM</t>
+          <t>CTR_CCE_WIDTH</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1718,33 +1808,35 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>range</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>An implementation may make field UBE be a read-only copy</t>
+          <t>may implement 0..4 exponent bits in CCE</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>hypervisor.adoc</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
+          <t>smctr.adoc</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>648</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>norm:ccounter_impl</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1752,67 +1844,70 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>An implementation may make field UBE be a read-only copy of `hstatus`.VSBE.</t>
-        </is>
-      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>parameter: new WARL  behavior! (ReadOnly, but value is the the value of some other state bit)</t>
+          <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE. Unimplemented CCE bits are read-only 0.</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>WARL behavior</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>DELEGATABLE_EXCEPTIONS</t>
+          <t>CTR_RASEMU_IMPLEMENTED</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>An implementation can choose to subset the delegatable traps</t>
+          <t>optional `__x__ctrctl`.RASEMU bit is implemented</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
+          <t>smctr.adoc</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>693</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>norm:medeleg_mideleg_warl</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:ctrctl_rasemu_op</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1820,110 +1915,118 @@
           <t>no</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>An implementation can choose to subset the delegatable traps, with the supported delegatable bits found by writing one to every bit location, then reading back the value in `medeleg` or `mideleg` to see which bit positions hold a one.</t>
-        </is>
-      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
+          <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>possibly a parameter; or WARL: depends on whether there is some other state bit that controls "RASEMU is implemented"; could as</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>MIP_WRITABLE_BITS</t>
+          <t>CTR_SUPPORTED_DEPTHS</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>NORM_CSR_RW</t>
+          <t>NORM_CSR_WARL</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>set</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>may be writable or may be read-only</t>
+          <t>implementation-specific which DEPTH value(s) are supported</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>machine.adoc</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
+          <t>smctr.adoc</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>222</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>norm:mip_bits_wr_or_rdonly</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:sctrdepth-depth_param</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>Each individual bit in register `mip` may be writable or may be read-only.</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
+          <t>It is implementation-specific which DEPTH value(s) are supported.</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>WPRI field, so effectively WARL behavior</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2. Mentor-confirmed (V3)</t>
+          <t>1. V4 - for review</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PMPADDR_WARL_MASK</t>
+          <t>MENVCFG_FIOM_READONLY</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>NORM_CSR_WARL</t>
+          <t>NORM_CSR_RW</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Not all physical address bits may be implemented</t>
+          <t>the implementation may make FIOM read-only zero</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1931,24 +2034,22 @@
           <t>machine.adoc</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
+      <c r="G23" s="3" t="n">
+        <v>1455</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>norm:pmp_addr_warl</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>norm:menvcfg_fiom_rdonly0_ok</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -1956,1088 +2057,1776 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>Not all physical address bits may be implemented, and so the `pmpaddr` registers are WARL.</t>
-        </is>
-      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>parameter: WARL  (number of implemented address bits; conditional on or priv mode and xSATP.mode (VA vs. PA)</t>
+          <t>If S-mode is not supported, or if `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>parameter (CSR is RW, but this allows it to be RdOnly0) under specific conditions</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>1. V4 - for review</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SENVCFG_FIOM_ACCESS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>NORM_CSR_RW</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>the implementation may make FIOM read-only zero</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>706</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>machine.adoc, supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duplicate of above </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>HPM_UNIMPLEMENTED_ACCESS_BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>may cause an illegal-instruction exception or may return a constant value</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>counters.adoc</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>norm:hpm_unimplemented_counter_access</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Accessing an unimplemented counter may cause an illegal-instruction exception or may return a constant value.</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>WARL parameter:  returning a constant value implies implemented, so which counters are implemented is the parameter, If unimplmented, requires illegal inst trap (NOT unspecified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>HPM_MISCONFIGURED_BEHAVIOR</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>the counter may return a constant value</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>counters.adoc</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>norm:hpm_misconfigured_event_behavior</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>If the configuration used to select the events counted by a counter is misconfigured, the counter may return a constant value.</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>parameter: WARL behavior (only tested if Ssstrict is implemented, else is unspeciifed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>VSXL_RO_PARAM</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>NORM_CSR_RW</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>an implementation may make VSXL be a read-only field</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>hypervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>norm:vsxl_ro_param</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>In particular, an implementation may make VSXL be a read-only field whose value always ensures that VSXLEN=HSXLEN.</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>new WARL parameter behavior! (ReadOnly, but value is the the value of some other state bit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>VTW_VIRTINSTR_PARAM</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>NORM_DIRECT</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>An implementation may have WFI always raise a virtual-instruction exception</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>hypervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>norm:vtw_virtinstr_param</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>An implementation may have WFI always raise a virtual-instruction exception in VS-mode when VTW=1 (and `mstatus`.TW=0), even if there are pending globally-disabled interrupts when the instruction is executed.</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>parameter: raise virt inst, or just wait?</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>VSSTATUS_UBE_PARAM</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>NORM_CSR_RW</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>An implementation may make field UBE be a read-only copy</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>hypervisor.adoc</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1226</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>An implementation may make field UBE be a read-only copy of `hstatus`.VSBE.</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>parameter: new WARL  behavior! (ReadOnly, but value is the the value of some other state bit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>DELEGATABLE_EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>NORM_CSR_WARL</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>bitmask</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>An implementation can choose to subset the delegatable traps</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1310</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>norm:medeleg_mideleg_warl</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>An implementation can choose to subset the delegatable traps, with the supported delegatable bits found by writing one to every bit location, then reading back the value in `medeleg` or `mideleg` to see which bit positions hold a one.</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>MIP_WRITABLE_BITS</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>NORM_CSR_RW</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>bitmask</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>may be writable or may be read-only</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1395</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>norm:mip_bits_wr_or_rdonly</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Each individual bit in register `mip` may be writable or may be read-only.</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>PMPADDR_WARL_MASK</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>NORM_CSR_WARL</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>bitmask</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Not all physical address bits may be implemented</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>machine.adoc</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>3395</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>norm:pmp_addr_warl</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Not all physical address bits may be implemented, and so the `pmpaddr` registers are WARL.</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>parameter: WARL  (number of implemented address bits; conditional on or priv mode and xSATP.mode (VA vs. PA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>2. Mentor-confirmed (V3)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>MNEPC_INVALID_ADDRESS_CONVERSION</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>implementations may convert an invalid address</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>rnmi.adoc</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="G33" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>norm:mnepc_invalid_convert</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Prior to writing `mnepc`, implementations may convert an invalid address into some other invalid address that `mnepc` is capable of holding.</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>parameter: WARL behavior ( but depends on definition of "invalid". Implies implemented&lt;full width.)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>MSECCFG_SEED_BITS_RW</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>may implement `mseccfg` such that `[s,u]seed` is a read-only constant value</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>scalar-crypto.adoc</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr">
+      <c r="G34" s="4" t="n">
+        <v>3750</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Implementations may implement `mseccfg` such that `[s,u]seed` is a read-only constant value `0`.</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (RW or RO0; RO1 not legal)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>SCTRDEPTH_SUPPORTED_VALUES</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_WARL</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>implementation-specific which DEPTH value(s) are supported</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="G35" s="4" t="n">
+        <v>189</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>norm:sctrdepth-depth_param</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>It is implementation-specific which DEPTH value(s) are supported.</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>parameter: WARL behavior (range value, or set)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>CTRTARGET_MISP_IMPLEMENTED</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>The optional MISP bit</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="G36" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>norm:ctrtarget_misp</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>The optional MISP bit is set by the hardware when the recorded transfer is an instruction whose target or taken/not-taken direction was mispredicted by the branch predictor. MISP is read-only 0 when not implemented.</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value is either fixed 0 or the the value of some *internal* status  bit)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>CTR_CYCLE_COUNTING_SUPPORTED</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>may optionally include a count of CPU cycles</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="G37" s="4" t="n">
+        <v>612</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>norm:ctrdata_cc_supported_param</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>The `ctrdata` register may optionally include a count of CPU cycles elapsed since the prior CTR record.</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>CTR_CCE_WIDTH</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>range</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>may implement 0..4 exponent bits in CCE</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="G38" s="4" t="n">
+        <v>638</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>norm:ccounter_impl</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>An implementation that supports cycle counting must implement CCV and all CCM bits, but may implement 0..4 exponent bits in CCE.</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>parameter (also in top-14 above)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>CTR_RASEMU_SUPPORTED</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>When the optional `__x__ctrctl`.RASEMU bit is implemented</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>smctr.adoc</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="G39" s="4" t="n">
+        <v>669</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>norm:ctrctl_rasemu_op</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>When the optional `__x__ctrctl`.RASEMU bit is implemented and set to 1, transfer recording behavior is altered to emulate the behavior of a return-address stack (RAS).</t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>STATEEN_IMPLICIT_UPDATE_EXCEPTION</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>may or may not raise an illegal-instruction or virtual-instruction exception</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>smstateen.adoc</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="G40" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>When a `stateen` CSR prevents access to state for a privilege mode, attempting to execute in that privilege mode an instruction that _implicitly_ updates the state without reading it may or may not raise an illegal-instruction or virtual-instruction exception.</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>parameter (trap or not; which kind of trap is defined elsewhere)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>SSTATUS_UXL_ACCESS</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>an implementation may make UXL be a read-only field</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr">
+      <c r="G41" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>When SXLEN=64, it is a *WARL* field that encodes the current value of UXLEN. In particular, an implementation may make UXL be a read-only field whose value always ensures that UXLEN=SXLEN.</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value includes the value of sother state bit)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>HINT_SXLEN_BEHAVIOR</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr">
+      <c r="G42" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>When such a HINT is executed with XLEN &lt; SXLEN and bits SXLEN..XLEN of the destination register not all equal to bit XLEN-1, it is implementation-defined whether bits SXLEN..XLEN of the destination register are unchanged or are overwritten with copies of bit XLEN-1.</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>SSTATUS_UBE_ACCESS</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>An implementation may make UBE be a read-only field</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="G43" s="4" t="n">
+        <v>221</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>An implementation may make UBE be a read-only field that always specifies the same endianness as for S-mode.</t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>new WARL parameter behavior! (ReadOnly, but value includes the value of some state  bit)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>SIP_BITS_ACCESS</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>bitmask</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>may be writable or may be read-only</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="G44" s="4" t="n">
+        <v>434</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>norm:sip_acc</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>Each individual bit in register `sip` may be writable or may be read-only.</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>WARL parameter (RW, RdOnly0/1)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>STANDARD_INTERRUPT_SUPPORT</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>bitmask</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>may not be implemented</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="G45" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>Each standard interrupt type (SEI, STI, SSI, or LCOFI) may not be implemented, in which case the corresponding interrupt-pending and interrupt-enable bits are read-only zeros.</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>WARL parameter (RW, RdOnly0)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>SENVCFG_FIOM_ACCESS</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>NORM_CSR_RW</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>the implementation may make FIOM read-only zero</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>supervisor.adoc</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>YES: machine.adoc, supervisor.adoc</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
+      <c r="G46" s="4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>machine.adoc, supervisor.adoc</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>If `satp`.MODE is read-only zero (always Bare), the implementation may make FIOM read-only zero.</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>WARL parameter: conditional on mode  (also in top-14 above)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ZALASR_MISALIGNED_ATOMICITY_GRANULE</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>binary</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>optionally relaxes this alignment requirement</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>zalasr.adoc</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="G47" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>norm:zalasr_misaligned_pma_relax</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t>YES: a-st-ext.adoc, zalasr.adoc</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>a-st-ext.adoc, zalasr.adoc</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>The misaligned atomicity granule PMA, defined in Volume II of this manual, optionally relaxes this alignment requirement.</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>parameter: (existence &amp; value of atomicity granule)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>2. Mentor-confirmed (V3)</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>CSR_STRONGLY_ORDERED</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>NORM_DIRECT</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>may define that accesses to certain CSRs are strongly ordered</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>zicsr.adoc</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G48" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>norm:csr_strongly_ordered</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>The hardware platform may define that accesses to certain CSRs are strongly ordered, as defined by the Memory-Ordering PMAs section in Volume II of this manual.</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>parameter: memory ordering PMA value(s)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N39"/>
+  <autoFilter ref="A1:O48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>